--- a/PVZ2.xlsx
+++ b/PVZ2.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agentura2020.sharepoint.com/sites/VidurioLietuvosaplinkostyrimuskyrius/Bendrai naudojami dokumentai/EB7-014 Darbuotojų failai/Tomo/Python 3.14.3/Skaiciavimai/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{9216244B-CFBA-4143-A519-E463F52612D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6945156-4103-492B-89A9-884392078EF5}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{9216244B-CFBA-4143-A519-E463F52612D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FAF6DEC-8B22-4391-B617-3B0A43BAF9E3}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Kk54ag9ImqTncQsqV7PcaNGRro/3kYoEKFl8q6vcBRTn3/Xg+oN1UCiXWk/LuUg3F3fng86CvkRAeYb6QmrkaA==" workbookSaltValue="ZcTpRu/F72OWXHaAa/zcKg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="821" firstSheet="1" activeTab="6" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="821" firstSheet="1" activeTab="2" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Compatibility Report" sheetId="4" state="hidden" r:id="rId1"/>
@@ -2357,93 +2357,97 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2493,10 +2497,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2938,18 +2938,18 @@
       <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A3" s="199" t="s">
+      <c r="A3" s="196" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="199"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="199"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="199"/>
-      <c r="I3" s="199"/>
-      <c r="J3" s="199"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="196"/>
+      <c r="H3" s="196"/>
+      <c r="I3" s="196"/>
+      <c r="J3" s="196"/>
     </row>
     <row r="4" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
@@ -3080,46 +3080,46 @@
       <c r="L10" s="42"/>
     </row>
     <row r="11" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H11" s="200" t="s">
+      <c r="H11" s="197" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="203" t="s">
+      <c r="I11" s="200" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H12" s="201"/>
-      <c r="I12" s="204"/>
+      <c r="H12" s="198"/>
+      <c r="I12" s="201"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H13" s="201"/>
-      <c r="I13" s="204"/>
+      <c r="H13" s="198"/>
+      <c r="I13" s="201"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H14" s="201"/>
-      <c r="I14" s="204"/>
+      <c r="H14" s="198"/>
+      <c r="I14" s="201"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H15" s="201"/>
-      <c r="I15" s="204"/>
+      <c r="H15" s="198"/>
+      <c r="I15" s="201"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H16" s="201"/>
-      <c r="I16" s="204"/>
+      <c r="H16" s="198"/>
+      <c r="I16" s="201"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="201"/>
-      <c r="I17" s="204"/>
+      <c r="H17" s="198"/>
+      <c r="I17" s="201"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="202"/>
-      <c r="I18" s="204"/>
+      <c r="H18" s="199"/>
+      <c r="I18" s="201"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I19" s="204"/>
+      <c r="I19" s="201"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I20" s="205"/>
+      <c r="I20" s="202"/>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:9" ht="14" x14ac:dyDescent="0.3">
@@ -3169,15 +3169,15 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="198" t="s">
+      <c r="A34" s="195" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="198"/>
-      <c r="C34" s="198"/>
-      <c r="D34" s="198"/>
-      <c r="E34" s="198"/>
-      <c r="F34" s="198"/>
-      <c r="G34" s="198"/>
+      <c r="B34" s="195"/>
+      <c r="C34" s="195"/>
+      <c r="D34" s="195"/>
+      <c r="E34" s="195"/>
+      <c r="F34" s="195"/>
+      <c r="G34" s="195"/>
       <c r="H34" s="178">
         <v>46024</v>
       </c>
@@ -3255,35 +3255,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="196" t="s">
+      <c r="C1" s="203" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="196"/>
+      <c r="D1" s="203"/>
       <c r="E1" s="15"/>
       <c r="S1" s="88"/>
     </row>
     <row r="2" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="213" t="s">
+      <c r="A2" s="204" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="213"/>
-      <c r="C2" s="213"/>
-      <c r="D2" s="213"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="213"/>
-      <c r="G2" s="213"/>
-      <c r="H2" s="213"/>
-      <c r="I2" s="213"/>
-      <c r="J2" s="213"/>
-      <c r="K2" s="213"/>
-      <c r="L2" s="213"/>
-      <c r="M2" s="213"/>
-      <c r="N2" s="213"/>
-      <c r="O2" s="213"/>
-      <c r="P2" s="213"/>
-      <c r="Q2" s="213"/>
-      <c r="R2" s="213"/>
-      <c r="S2" s="213"/>
+      <c r="B2" s="204"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
+      <c r="I2" s="204"/>
+      <c r="J2" s="204"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="204"/>
+      <c r="M2" s="204"/>
+      <c r="N2" s="204"/>
+      <c r="O2" s="204"/>
+      <c r="P2" s="204"/>
+      <c r="Q2" s="204"/>
+      <c r="R2" s="204"/>
+      <c r="S2" s="204"/>
     </row>
     <row r="3" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="89"/>
@@ -3385,7 +3385,7 @@
       <c r="B6" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="203" t="s">
+      <c r="C6" s="200" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="139"/>
@@ -3427,7 +3427,7 @@
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="35"/>
       <c r="B7" s="32"/>
-      <c r="C7" s="204"/>
+      <c r="C7" s="201"/>
       <c r="D7" s="17"/>
       <c r="E7" s="18"/>
       <c r="F7" s="60" t="e">
@@ -3463,7 +3463,7 @@
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="B8" s="32"/>
-      <c r="C8" s="204"/>
+      <c r="C8" s="201"/>
       <c r="D8" s="17"/>
       <c r="E8" s="18"/>
       <c r="F8" s="60" t="e">
@@ -3499,7 +3499,7 @@
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="B9" s="32"/>
-      <c r="C9" s="204"/>
+      <c r="C9" s="201"/>
       <c r="D9" s="93"/>
       <c r="E9" s="93"/>
       <c r="F9" s="60" t="e">
@@ -3544,7 +3544,7 @@
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="93"/>
       <c r="B10" s="93"/>
-      <c r="C10" s="204"/>
+      <c r="C10" s="201"/>
       <c r="D10" s="93"/>
       <c r="E10" s="93"/>
       <c r="F10" s="60" t="e">
@@ -3573,20 +3573,20 @@
       </c>
       <c r="R10" s="93"/>
       <c r="S10" s="93"/>
-      <c r="T10" s="210" t="s">
+      <c r="T10" s="209" t="s">
         <v>33</v>
       </c>
-      <c r="U10" s="210" t="s">
+      <c r="U10" s="209" t="s">
         <v>34</v>
       </c>
-      <c r="V10" s="209" t="s">
+      <c r="V10" s="208" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="93"/>
       <c r="B11" s="93"/>
-      <c r="C11" s="204"/>
+      <c r="C11" s="201"/>
       <c r="D11" s="93"/>
       <c r="E11" s="93"/>
       <c r="F11" s="60" t="e">
@@ -3615,14 +3615,14 @@
       </c>
       <c r="R11" s="93"/>
       <c r="S11" s="93"/>
-      <c r="T11" s="211"/>
-      <c r="U11" s="211"/>
-      <c r="V11" s="209"/>
+      <c r="T11" s="210"/>
+      <c r="U11" s="210"/>
+      <c r="V11" s="208"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="93"/>
       <c r="B12" s="93"/>
-      <c r="C12" s="204"/>
+      <c r="C12" s="201"/>
       <c r="D12" s="93"/>
       <c r="E12" s="93"/>
       <c r="F12" s="60" t="e">
@@ -3651,14 +3651,14 @@
       </c>
       <c r="R12" s="93"/>
       <c r="S12" s="93"/>
-      <c r="T12" s="212"/>
-      <c r="U12" s="212"/>
-      <c r="V12" s="209"/>
+      <c r="T12" s="211"/>
+      <c r="U12" s="211"/>
+      <c r="V12" s="208"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="93"/>
       <c r="B13" s="93"/>
-      <c r="C13" s="204"/>
+      <c r="C13" s="201"/>
       <c r="D13" s="93"/>
       <c r="E13" s="93"/>
       <c r="F13" s="60" t="e">
@@ -3691,7 +3691,7 @@
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="94"/>
       <c r="B14" s="94"/>
-      <c r="C14" s="205"/>
+      <c r="C14" s="202"/>
       <c r="D14" s="94"/>
       <c r="E14" s="94"/>
       <c r="F14" s="60" t="e">
@@ -3789,19 +3789,19 @@
       <c r="A28" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="F28" s="208">
+      <c r="F28" s="207">
         <v>46024</v>
       </c>
-      <c r="G28" s="208"/>
+      <c r="G28" s="207"/>
       <c r="H28" s="37" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F29" s="207" t="s">
+      <c r="F29" s="206" t="s">
         <v>116</v>
       </c>
-      <c r="G29" s="207"/>
+      <c r="G29" s="206"/>
       <c r="H29" s="87" t="s">
         <v>117</v>
       </c>
@@ -3812,19 +3812,19 @@
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H31" s="206">
+      <c r="H31" s="205">
         <v>46024</v>
       </c>
-      <c r="I31" s="206"/>
+      <c r="I31" s="205"/>
       <c r="J31" s="87" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H32" s="207" t="s">
+      <c r="H32" s="206" t="s">
         <v>119</v>
       </c>
-      <c r="I32" s="207"/>
+      <c r="I32" s="206"/>
       <c r="J32" s="87" t="s">
         <v>117</v>
       </c>
@@ -3851,8 +3851,11 @@
       <c r="B98" s="96"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1LUdbAtr+2ZmdyZ8Y8MO8jkzDRdfoKk0lc0JEmIslWWzvsoemJo26G6OJ/3thwZr9i1JylrthkKzRWbw5KXGtg==" saltValue="req8evI/XNzuA4VUJfkc1Q==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="10">
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="T10:T12"/>
+    <mergeCell ref="U10:U12"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="C6:C14"/>
@@ -3860,9 +3863,6 @@
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="T10:T12"/>
-    <mergeCell ref="U10:U12"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.19685039370078741" right="0" top="0.74803149606299213" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3899,26 +3899,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="196" t="s">
+      <c r="C1" s="203" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="196"/>
+      <c r="D1" s="203"/>
       <c r="Q1" s="16"/>
     </row>
     <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="214"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="214"/>
-      <c r="I2" s="214"/>
-      <c r="J2" s="214"/>
-      <c r="K2" s="214"/>
-      <c r="L2" s="214"/>
-      <c r="M2" s="214"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
       <c r="Q2" s="16"/>
     </row>
     <row r="3" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -3980,7 +3980,7 @@
         <f>Paėmimas!B6</f>
         <v>XX</v>
       </c>
-      <c r="C6" s="215" t="str">
+      <c r="C6" s="213" t="str">
         <f>Paėmimas!C6</f>
         <v>UAB ,,XXX". Taršos šaltinis Nr. 001.</v>
       </c>
@@ -4032,7 +4032,7 @@
     <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="51"/>
       <c r="B7" s="21"/>
-      <c r="C7" s="216"/>
+      <c r="C7" s="214"/>
       <c r="D7" s="50">
         <f>Paėmimas!L7</f>
         <v>0</v>
@@ -4069,7 +4069,7 @@
     <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="51"/>
       <c r="B8" s="21"/>
-      <c r="C8" s="216"/>
+      <c r="C8" s="214"/>
       <c r="D8" s="50">
         <f>Paėmimas!L8</f>
         <v>0</v>
@@ -4106,7 +4106,7 @@
     <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="51"/>
       <c r="B9" s="21"/>
-      <c r="C9" s="216"/>
+      <c r="C9" s="214"/>
       <c r="D9" s="50">
         <f>Paėmimas!L9</f>
         <v>0</v>
@@ -4143,7 +4143,7 @@
     <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="51"/>
       <c r="B10" s="21"/>
-      <c r="C10" s="216"/>
+      <c r="C10" s="214"/>
       <c r="D10" s="50">
         <f>Paėmimas!L10</f>
         <v>0</v>
@@ -4180,7 +4180,7 @@
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="51"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="216"/>
+      <c r="C11" s="214"/>
       <c r="D11" s="50">
         <f>Paėmimas!L11</f>
         <v>0</v>
@@ -4217,7 +4217,7 @@
     <row r="12" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="51"/>
       <c r="B12" s="21"/>
-      <c r="C12" s="216"/>
+      <c r="C12" s="214"/>
       <c r="D12" s="50">
         <f>Paėmimas!L12</f>
         <v>0</v>
@@ -4254,7 +4254,7 @@
     <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="51"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="216"/>
+      <c r="C13" s="214"/>
       <c r="D13" s="50">
         <f>Paėmimas!L13</f>
         <v>0</v>
@@ -4291,7 +4291,7 @@
     <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="53"/>
       <c r="B14" s="54"/>
-      <c r="C14" s="217"/>
+      <c r="C14" s="215"/>
       <c r="D14" s="61">
         <f>Paėmimas!L14</f>
         <v>0</v>
@@ -4497,29 +4497,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="196" t="s">
+      <c r="C1" s="203" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="196"/>
+      <c r="D1" s="203"/>
       <c r="R1" s="16"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="197" t="s">
+      <c r="A2" s="218" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="197"/>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="197"/>
-      <c r="G2" s="197"/>
-      <c r="H2" s="197"/>
-      <c r="I2" s="197"/>
-      <c r="J2" s="197"/>
-      <c r="K2" s="197"/>
-      <c r="L2" s="197"/>
-      <c r="M2" s="197"/>
-      <c r="N2" s="197"/>
+      <c r="B2" s="218"/>
+      <c r="C2" s="218"/>
+      <c r="D2" s="218"/>
+      <c r="E2" s="218"/>
+      <c r="F2" s="218"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
+      <c r="J2" s="218"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="218"/>
+      <c r="M2" s="218"/>
+      <c r="N2" s="218"/>
       <c r="O2" s="147"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -4590,7 +4590,7 @@
         <f>Svėrimas!A6</f>
         <v>XXXXX</v>
       </c>
-      <c r="C6" s="194" t="str">
+      <c r="C6" s="216" t="str">
         <f>Paėmimas!C6</f>
         <v>UAB ,,XXX". Taršos šaltinis Nr. 001.</v>
       </c>
@@ -4649,7 +4649,7 @@
     <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="161"/>
       <c r="B7" s="163"/>
-      <c r="C7" s="194"/>
+      <c r="C7" s="216"/>
       <c r="D7" s="177"/>
       <c r="E7" s="142"/>
       <c r="F7" s="57"/>
@@ -4667,7 +4667,7 @@
     <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="162"/>
       <c r="B8" s="159"/>
-      <c r="C8" s="195"/>
+      <c r="C8" s="217"/>
       <c r="D8" s="177"/>
       <c r="E8" s="142"/>
       <c r="F8" s="57"/>
@@ -5119,77 +5119,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="196" t="s">
+      <c r="C1" s="203" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="196"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="196"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
     </row>
     <row r="2" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="214" t="s">
+      <c r="A2" s="212" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="214"/>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="214"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="214"/>
-      <c r="I2" s="214"/>
-      <c r="J2" s="214"/>
-      <c r="K2" s="214"/>
-      <c r="L2" s="214"/>
-      <c r="M2" s="214"/>
-      <c r="N2" s="214"/>
-      <c r="O2" s="214"/>
+      <c r="B2" s="212"/>
+      <c r="C2" s="212"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
+      <c r="N2" s="212"/>
+      <c r="O2" s="212"/>
       <c r="V2" s="16"/>
     </row>
     <row r="4" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="221" t="s">
+      <c r="A4" s="222" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="221" t="s">
+      <c r="B4" s="222" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="229" t="s">
+      <c r="C4" s="230" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="229" t="s">
+      <c r="D4" s="230" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="229" t="s">
+      <c r="E4" s="230" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="229"/>
-      <c r="G4" s="229"/>
-      <c r="H4" s="229" t="s">
+      <c r="F4" s="230"/>
+      <c r="G4" s="230"/>
+      <c r="H4" s="230" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="226" t="s">
         <v>85</v>
       </c>
-      <c r="J4" s="220" t="s">
+      <c r="J4" s="221" t="s">
         <v>86</v>
       </c>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
-      <c r="M4" s="227" t="s">
+      <c r="K4" s="221"/>
+      <c r="L4" s="221"/>
+      <c r="M4" s="228" t="s">
         <v>122</v>
       </c>
-      <c r="N4" s="220" t="s">
+      <c r="N4" s="221" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="223" t="s">
+      <c r="O4" s="224" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="222"/>
-      <c r="B5" s="222"/>
-      <c r="C5" s="230"/>
-      <c r="D5" s="229"/>
+      <c r="A5" s="223"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="231"/>
+      <c r="D5" s="230"/>
       <c r="E5" s="120">
         <v>1</v>
       </c>
@@ -5199,8 +5199,8 @@
       <c r="G5" s="120">
         <v>3</v>
       </c>
-      <c r="H5" s="229"/>
-      <c r="I5" s="226"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="227"/>
       <c r="J5" s="12">
         <v>1</v>
       </c>
@@ -5210,15 +5210,15 @@
       <c r="L5" s="12">
         <v>3</v>
       </c>
-      <c r="M5" s="228"/>
-      <c r="N5" s="220"/>
-      <c r="O5" s="224"/>
+      <c r="M5" s="229"/>
+      <c r="N5" s="221"/>
+      <c r="O5" s="225"/>
     </row>
     <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="218" t="str">
+      <c r="B6" s="219" t="str">
         <f>Paėmimas!C6</f>
         <v>UAB ,,XXX". Taršos šaltinis Nr. 001.</v>
       </c>
@@ -5256,7 +5256,7 @@
     </row>
     <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="85"/>
-      <c r="B7" s="218"/>
+      <c r="B7" s="219"/>
       <c r="C7" s="30"/>
       <c r="D7" s="28"/>
       <c r="E7" s="168"/>
@@ -5276,7 +5276,7 @@
     </row>
     <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="85"/>
-      <c r="B8" s="218"/>
+      <c r="B8" s="219"/>
       <c r="C8" s="30"/>
       <c r="D8" s="80"/>
       <c r="E8" s="168"/>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="9" spans="1:22" ht="17" x14ac:dyDescent="0.45">
       <c r="A9" s="85"/>
-      <c r="B9" s="218"/>
+      <c r="B9" s="219"/>
       <c r="C9" s="30">
         <v>39</v>
       </c>
@@ -5321,7 +5321,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="85"/>
-      <c r="B10" s="218"/>
+      <c r="B10" s="219"/>
       <c r="C10" s="30"/>
       <c r="D10" s="80"/>
       <c r="E10" s="168"/>
@@ -5338,7 +5338,7 @@
     </row>
     <row r="11" spans="1:22" ht="17" x14ac:dyDescent="0.45">
       <c r="A11" s="85"/>
-      <c r="B11" s="218"/>
+      <c r="B11" s="219"/>
       <c r="C11" s="30">
         <v>40</v>
       </c>
@@ -5362,7 +5362,7 @@
     </row>
     <row r="12" spans="1:22" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="85"/>
-      <c r="B12" s="218"/>
+      <c r="B12" s="219"/>
       <c r="C12" s="114" t="s">
         <v>43</v>
       </c>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="13" spans="1:22" ht="17" x14ac:dyDescent="0.45">
       <c r="A13" s="85"/>
-      <c r="B13" s="218"/>
+      <c r="B13" s="219"/>
       <c r="C13" s="115" t="s">
         <v>44</v>
       </c>
@@ -5410,7 +5410,7 @@
     </row>
     <row r="14" spans="1:22" ht="17" x14ac:dyDescent="0.45">
       <c r="A14" s="85"/>
-      <c r="B14" s="218"/>
+      <c r="B14" s="219"/>
       <c r="C14" s="115" t="s">
         <v>45</v>
       </c>
@@ -5434,7 +5434,7 @@
     </row>
     <row r="15" spans="1:22" ht="17" x14ac:dyDescent="0.45">
       <c r="A15" s="85"/>
-      <c r="B15" s="218"/>
+      <c r="B15" s="219"/>
       <c r="C15" s="116" t="s">
         <v>46</v>
       </c>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="16" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="86"/>
-      <c r="B16" s="219"/>
+      <c r="B16" s="220"/>
       <c r="C16" s="30"/>
       <c r="D16" s="81"/>
       <c r="E16" s="19"/>
@@ -5802,12 +5802,12 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="231" t="s">
+      <c r="A3" s="194" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="231"/>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="194"/>
     </row>
     <row r="5" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="107" t="s">
@@ -5851,26 +5851,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
     <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
@@ -6125,10 +6105,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605DD0A7-BC00-4D8E-8AD3-26E2A9FDEA54}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58161107-3028-416E-B6BD-4D514713B3D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6145,20 +6156,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58161107-3028-416E-B6BD-4D514713B3D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605DD0A7-BC00-4D8E-8AD3-26E2A9FDEA54}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
-    <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/PVZ2.xlsx
+++ b/PVZ2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agentura2020.sharepoint.com/sites/VidurioLietuvosaplinkostyrimuskyrius/Bendrai naudojami dokumentai/EB7-014 Darbuotojų failai/Tomo/Python 3.14.3/Skaiciavimai/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{8FD3B17B-922A-42A3-879B-A575A223ADA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83F9F1B0-3FD9-4D44-B0EB-12D8C7A1554E}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="8_{8FD3B17B-922A-42A3-879B-A575A223ADA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D4044E6-60E2-4BF7-BDD4-4F820AD5D73A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="821" firstSheet="1" activeTab="1" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="821" firstSheet="1" activeTab="2" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Compatibility Report" sheetId="4" state="hidden" r:id="rId1"/>
@@ -2658,6 +2658,141 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="29" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2667,14 +2802,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2718,133 +2845,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="29" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3283,31 +3283,31 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="D3" s="273" t="s">
+      <c r="D3" s="262" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="273"/>
-      <c r="F3" s="273"/>
-      <c r="G3" s="273"/>
-      <c r="H3" s="273"/>
-      <c r="I3" s="273"/>
-      <c r="J3" s="273"/>
-      <c r="K3" s="273"/>
-      <c r="L3" s="273"/>
-      <c r="M3" s="273"/>
-      <c r="N3" s="273"/>
-      <c r="O3" s="273"/>
-      <c r="P3" s="273"/>
-      <c r="Q3" s="273"/>
-      <c r="R3" s="273"/>
-      <c r="S3" s="273"/>
-      <c r="T3" s="273"/>
-      <c r="U3" s="273"/>
-      <c r="V3" s="273"/>
-      <c r="W3" s="273"/>
-      <c r="X3" s="273"/>
-      <c r="Y3" s="273"/>
-      <c r="Z3" s="273"/>
+      <c r="E3" s="262"/>
+      <c r="F3" s="262"/>
+      <c r="G3" s="262"/>
+      <c r="H3" s="262"/>
+      <c r="I3" s="262"/>
+      <c r="J3" s="262"/>
+      <c r="K3" s="262"/>
+      <c r="L3" s="262"/>
+      <c r="M3" s="262"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="262"/>
+      <c r="P3" s="262"/>
+      <c r="Q3" s="262"/>
+      <c r="R3" s="262"/>
+      <c r="S3" s="262"/>
+      <c r="T3" s="262"/>
+      <c r="U3" s="262"/>
+      <c r="V3" s="262"/>
+      <c r="W3" s="262"/>
+      <c r="X3" s="262"/>
+      <c r="Y3" s="262"/>
+      <c r="Z3" s="262"/>
     </row>
     <row r="5" spans="1:28" s="10" customFormat="1" ht="126" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
@@ -3396,13 +3396,13 @@
       </c>
     </row>
     <row r="6" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="274" t="s">
+      <c r="A6" s="263" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="277" t="s">
+      <c r="B6" s="266" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="278" t="s">
+      <c r="C6" s="267" t="s">
         <v>140</v>
       </c>
       <c r="D6" s="127">
@@ -3488,14 +3488,14 @@
         <f>Aerodinamika!G23</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="AB6" s="271" t="s">
+      <c r="AB6" s="260" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="275"/>
-      <c r="B7" s="275"/>
-      <c r="C7" s="279"/>
+      <c r="A7" s="264"/>
+      <c r="B7" s="264"/>
+      <c r="C7" s="268"/>
       <c r="D7" s="127">
         <v>19</v>
       </c>
@@ -3575,12 +3575,12 @@
         <f>O6*X7</f>
         <v>0.34740732161375365</v>
       </c>
-      <c r="AB7" s="272"/>
+      <c r="AB7" s="261"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="275"/>
-      <c r="B8" s="275"/>
-      <c r="C8" s="279"/>
+      <c r="A8" s="264"/>
+      <c r="B8" s="264"/>
+      <c r="C8" s="268"/>
       <c r="D8" s="254">
         <v>33</v>
       </c>
@@ -3626,9 +3626,9 @@
       <c r="S8" s="126"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="275"/>
-      <c r="B9" s="275"/>
-      <c r="C9" s="279"/>
+      <c r="A9" s="264"/>
+      <c r="B9" s="264"/>
+      <c r="C9" s="268"/>
       <c r="D9" s="127">
         <v>48</v>
       </c>
@@ -3678,9 +3678,9 @@
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="275"/>
-      <c r="B10" s="275"/>
-      <c r="C10" s="279"/>
+      <c r="A10" s="264"/>
+      <c r="B10" s="264"/>
+      <c r="C10" s="268"/>
       <c r="D10" s="127">
         <v>65</v>
       </c>
@@ -3719,9 +3719,9 @@
       <c r="N10" s="179"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="275"/>
-      <c r="B11" s="275"/>
-      <c r="C11" s="279"/>
+      <c r="A11" s="264"/>
+      <c r="B11" s="264"/>
+      <c r="C11" s="268"/>
       <c r="D11" s="127">
         <v>85</v>
       </c>
@@ -3760,9 +3760,9 @@
       <c r="N11" s="179"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="275"/>
-      <c r="B12" s="275"/>
-      <c r="C12" s="279"/>
+      <c r="A12" s="264"/>
+      <c r="B12" s="264"/>
+      <c r="C12" s="268"/>
       <c r="D12" s="127">
         <v>108</v>
       </c>
@@ -3801,9 +3801,9 @@
       <c r="N12" s="179"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="275"/>
-      <c r="B13" s="275"/>
-      <c r="C13" s="279"/>
+      <c r="A13" s="264"/>
+      <c r="B13" s="264"/>
+      <c r="C13" s="268"/>
       <c r="D13" s="127">
         <v>140</v>
       </c>
@@ -3843,9 +3843,9 @@
       <c r="O13" s="124"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="275"/>
-      <c r="B14" s="275"/>
-      <c r="C14" s="279"/>
+      <c r="A14" s="264"/>
+      <c r="B14" s="264"/>
+      <c r="C14" s="268"/>
       <c r="D14" s="127">
         <v>200</v>
       </c>
@@ -3888,9 +3888,9 @@
       <c r="U14" s="37"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="275"/>
-      <c r="B15" s="275"/>
-      <c r="C15" s="279"/>
+      <c r="A15" s="264"/>
+      <c r="B15" s="264"/>
+      <c r="C15" s="268"/>
       <c r="D15" s="127">
         <v>260</v>
       </c>
@@ -3933,9 +3933,9 @@
       <c r="U15" s="37"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="275"/>
-      <c r="B16" s="275"/>
-      <c r="C16" s="279"/>
+      <c r="A16" s="264"/>
+      <c r="B16" s="264"/>
+      <c r="C16" s="268"/>
       <c r="D16" s="127">
         <v>292</v>
       </c>
@@ -3978,9 +3978,9 @@
       <c r="U16" s="37"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="275"/>
-      <c r="B17" s="275"/>
-      <c r="C17" s="279"/>
+      <c r="A17" s="264"/>
+      <c r="B17" s="264"/>
+      <c r="C17" s="268"/>
       <c r="D17" s="127">
         <v>315</v>
       </c>
@@ -4023,9 +4023,9 @@
       <c r="U17" s="37"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="275"/>
-      <c r="B18" s="275"/>
-      <c r="C18" s="279"/>
+      <c r="A18" s="264"/>
+      <c r="B18" s="264"/>
+      <c r="C18" s="268"/>
       <c r="D18" s="127">
         <v>335</v>
       </c>
@@ -4068,9 +4068,9 @@
       <c r="U18" s="37"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="275"/>
-      <c r="B19" s="275"/>
-      <c r="C19" s="279"/>
+      <c r="A19" s="264"/>
+      <c r="B19" s="264"/>
+      <c r="C19" s="268"/>
       <c r="D19" s="127">
         <v>352</v>
       </c>
@@ -4113,9 +4113,9 @@
       <c r="U19" s="37"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="275"/>
-      <c r="B20" s="275"/>
-      <c r="C20" s="279"/>
+      <c r="A20" s="264"/>
+      <c r="B20" s="264"/>
+      <c r="C20" s="268"/>
       <c r="D20" s="127">
         <v>367</v>
       </c>
@@ -4158,9 +4158,9 @@
       <c r="U20" s="37"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="275"/>
-      <c r="B21" s="275"/>
-      <c r="C21" s="279"/>
+      <c r="A21" s="264"/>
+      <c r="B21" s="264"/>
+      <c r="C21" s="268"/>
       <c r="D21" s="127">
         <v>381</v>
       </c>
@@ -4203,9 +4203,9 @@
       <c r="U21" s="37"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="276"/>
-      <c r="B22" s="276"/>
-      <c r="C22" s="280"/>
+      <c r="A22" s="265"/>
+      <c r="B22" s="265"/>
+      <c r="C22" s="269"/>
       <c r="D22" s="127">
         <v>394</v>
       </c>
@@ -4309,11 +4309,11 @@
         <v>0</v>
       </c>
       <c r="N24" s="69"/>
-      <c r="O24" s="281" t="s">
+      <c r="O24" s="270" t="s">
         <v>127</v>
       </c>
-      <c r="P24" s="282"/>
-      <c r="Q24" s="282"/>
+      <c r="P24" s="271"/>
+      <c r="Q24" s="271"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="157"/>
@@ -4348,30 +4348,30 @@
       <c r="A28" s="157"/>
       <c r="B28" s="157"/>
       <c r="C28" s="157"/>
-      <c r="D28" s="283" t="s">
+      <c r="D28" s="272" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="273"/>
-      <c r="F28" s="273"/>
-      <c r="G28" s="273"/>
-      <c r="H28" s="273"/>
-      <c r="I28" s="273"/>
-      <c r="J28" s="273"/>
-      <c r="K28" s="273"/>
-      <c r="L28" s="273"/>
-      <c r="M28" s="273"/>
-      <c r="N28" s="273"/>
-      <c r="O28" s="273"/>
-      <c r="P28" s="273"/>
-      <c r="Q28" s="273"/>
-      <c r="R28" s="273"/>
-      <c r="S28" s="273"/>
-      <c r="T28" s="273"/>
-      <c r="U28" s="273"/>
-      <c r="V28" s="273"/>
-      <c r="W28" s="273"/>
-      <c r="X28" s="273"/>
-      <c r="Y28" s="273"/>
+      <c r="E28" s="262"/>
+      <c r="F28" s="262"/>
+      <c r="G28" s="262"/>
+      <c r="H28" s="262"/>
+      <c r="I28" s="262"/>
+      <c r="J28" s="262"/>
+      <c r="K28" s="262"/>
+      <c r="L28" s="262"/>
+      <c r="M28" s="262"/>
+      <c r="N28" s="262"/>
+      <c r="O28" s="262"/>
+      <c r="P28" s="262"/>
+      <c r="Q28" s="262"/>
+      <c r="R28" s="262"/>
+      <c r="S28" s="262"/>
+      <c r="T28" s="262"/>
+      <c r="U28" s="262"/>
+      <c r="V28" s="262"/>
+      <c r="W28" s="262"/>
+      <c r="X28" s="262"/>
+      <c r="Y28" s="262"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="157"/>
@@ -4476,9 +4476,9 @@
       </c>
     </row>
     <row r="31" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="284"/>
-      <c r="B31" s="284"/>
-      <c r="C31" s="284"/>
+      <c r="A31" s="273"/>
+      <c r="B31" s="273"/>
+      <c r="C31" s="273"/>
       <c r="D31" s="127">
         <v>6</v>
       </c>
@@ -4556,12 +4556,12 @@
         <f>Aerodinamika!G23</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="AB31" s="271"/>
+      <c r="AB31" s="260"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A32" s="285"/>
-      <c r="B32" s="285"/>
-      <c r="C32" s="285"/>
+      <c r="A32" s="274"/>
+      <c r="B32" s="274"/>
+      <c r="C32" s="274"/>
       <c r="D32" s="127">
         <v>19</v>
       </c>
@@ -4632,12 +4632,12 @@
         <f>O31*X32</f>
         <v>0.34740732161375365</v>
       </c>
-      <c r="AB32" s="272"/>
+      <c r="AB32" s="261"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A33" s="285"/>
-      <c r="B33" s="285"/>
-      <c r="C33" s="285"/>
+      <c r="A33" s="274"/>
+      <c r="B33" s="274"/>
+      <c r="C33" s="274"/>
       <c r="D33" s="254">
         <v>33</v>
       </c>
@@ -4674,9 +4674,9 @@
       <c r="S33" s="126"/>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A34" s="285"/>
-      <c r="B34" s="285"/>
-      <c r="C34" s="285"/>
+      <c r="A34" s="274"/>
+      <c r="B34" s="274"/>
+      <c r="C34" s="274"/>
       <c r="D34" s="127">
         <v>48</v>
       </c>
@@ -4717,9 +4717,9 @@
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A35" s="285"/>
-      <c r="B35" s="285"/>
-      <c r="C35" s="285"/>
+      <c r="A35" s="274"/>
+      <c r="B35" s="274"/>
+      <c r="C35" s="274"/>
       <c r="D35" s="127">
         <v>65</v>
       </c>
@@ -4749,9 +4749,9 @@
       <c r="N35" s="133"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A36" s="285"/>
-      <c r="B36" s="285"/>
-      <c r="C36" s="285"/>
+      <c r="A36" s="274"/>
+      <c r="B36" s="274"/>
+      <c r="C36" s="274"/>
       <c r="D36" s="127">
         <v>85</v>
       </c>
@@ -4781,9 +4781,9 @@
       <c r="N36" s="133"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A37" s="285"/>
-      <c r="B37" s="285"/>
-      <c r="C37" s="285"/>
+      <c r="A37" s="274"/>
+      <c r="B37" s="274"/>
+      <c r="C37" s="274"/>
       <c r="D37" s="127">
         <v>108</v>
       </c>
@@ -4813,9 +4813,9 @@
       <c r="N37" s="133"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A38" s="285"/>
-      <c r="B38" s="285"/>
-      <c r="C38" s="285"/>
+      <c r="A38" s="274"/>
+      <c r="B38" s="274"/>
+      <c r="C38" s="274"/>
       <c r="D38" s="127">
         <v>140</v>
       </c>
@@ -4846,9 +4846,9 @@
       <c r="O38" s="124"/>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A39" s="285"/>
-      <c r="B39" s="285"/>
-      <c r="C39" s="285"/>
+      <c r="A39" s="274"/>
+      <c r="B39" s="274"/>
+      <c r="C39" s="274"/>
       <c r="D39" s="127">
         <v>200</v>
       </c>
@@ -4882,9 +4882,9 @@
       <c r="U39" s="37"/>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A40" s="285"/>
-      <c r="B40" s="285"/>
-      <c r="C40" s="285"/>
+      <c r="A40" s="274"/>
+      <c r="B40" s="274"/>
+      <c r="C40" s="274"/>
       <c r="D40" s="127">
         <v>260</v>
       </c>
@@ -4914,9 +4914,9 @@
       <c r="N40" s="127"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A41" s="285"/>
-      <c r="B41" s="285"/>
-      <c r="C41" s="285"/>
+      <c r="A41" s="274"/>
+      <c r="B41" s="274"/>
+      <c r="C41" s="274"/>
       <c r="D41" s="127">
         <v>292</v>
       </c>
@@ -4946,9 +4946,9 @@
       <c r="N41" s="127"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A42" s="285"/>
-      <c r="B42" s="285"/>
-      <c r="C42" s="285"/>
+      <c r="A42" s="274"/>
+      <c r="B42" s="274"/>
+      <c r="C42" s="274"/>
       <c r="D42" s="127">
         <v>315</v>
       </c>
@@ -4978,9 +4978,9 @@
       <c r="N42" s="127"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A43" s="285"/>
-      <c r="B43" s="285"/>
-      <c r="C43" s="285"/>
+      <c r="A43" s="274"/>
+      <c r="B43" s="274"/>
+      <c r="C43" s="274"/>
       <c r="D43" s="127">
         <v>335</v>
       </c>
@@ -5010,9 +5010,9 @@
       <c r="N43" s="127"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A44" s="285"/>
-      <c r="B44" s="285"/>
-      <c r="C44" s="285"/>
+      <c r="A44" s="274"/>
+      <c r="B44" s="274"/>
+      <c r="C44" s="274"/>
       <c r="D44" s="127">
         <v>352</v>
       </c>
@@ -5042,9 +5042,9 @@
       <c r="N44" s="127"/>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A45" s="285"/>
-      <c r="B45" s="285"/>
-      <c r="C45" s="285"/>
+      <c r="A45" s="274"/>
+      <c r="B45" s="274"/>
+      <c r="C45" s="274"/>
       <c r="D45" s="127">
         <v>367</v>
       </c>
@@ -5074,9 +5074,9 @@
       <c r="N45" s="127"/>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A46" s="285"/>
-      <c r="B46" s="285"/>
-      <c r="C46" s="285"/>
+      <c r="A46" s="274"/>
+      <c r="B46" s="274"/>
+      <c r="C46" s="274"/>
       <c r="D46" s="127">
         <v>381</v>
       </c>
@@ -5106,9 +5106,9 @@
       <c r="N46" s="127"/>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A47" s="286"/>
-      <c r="B47" s="286"/>
-      <c r="C47" s="286"/>
+      <c r="A47" s="275"/>
+      <c r="B47" s="275"/>
+      <c r="C47" s="275"/>
       <c r="D47" s="127">
         <v>394</v>
       </c>
@@ -5196,18 +5196,18 @@
       <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A3" s="287" t="s">
+      <c r="A3" s="276" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="287"/>
-      <c r="C3" s="287"/>
-      <c r="D3" s="287"/>
-      <c r="E3" s="287"/>
-      <c r="F3" s="287"/>
-      <c r="G3" s="287"/>
-      <c r="H3" s="287"/>
-      <c r="I3" s="287"/>
-      <c r="J3" s="287"/>
+      <c r="B3" s="276"/>
+      <c r="C3" s="276"/>
+      <c r="D3" s="276"/>
+      <c r="E3" s="276"/>
+      <c r="F3" s="276"/>
+      <c r="G3" s="276"/>
+      <c r="H3" s="276"/>
+      <c r="I3" s="276"/>
+      <c r="J3" s="276"/>
     </row>
     <row r="4" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
@@ -5354,46 +5354,46 @@
       <c r="L10" s="44"/>
     </row>
     <row r="11" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H11" s="288" t="s">
+      <c r="H11" s="277" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="291" t="s">
+      <c r="I11" s="280" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H12" s="289"/>
-      <c r="I12" s="292"/>
+      <c r="H12" s="278"/>
+      <c r="I12" s="281"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H13" s="289"/>
-      <c r="I13" s="292"/>
+      <c r="H13" s="278"/>
+      <c r="I13" s="281"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H14" s="289"/>
-      <c r="I14" s="292"/>
+      <c r="H14" s="278"/>
+      <c r="I14" s="281"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H15" s="289"/>
-      <c r="I15" s="292"/>
+      <c r="H15" s="278"/>
+      <c r="I15" s="281"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H16" s="289"/>
-      <c r="I16" s="292"/>
+      <c r="H16" s="278"/>
+      <c r="I16" s="281"/>
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="289"/>
-      <c r="I17" s="292"/>
+      <c r="H17" s="278"/>
+      <c r="I17" s="281"/>
     </row>
     <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="290"/>
-      <c r="I18" s="292"/>
+      <c r="H18" s="279"/>
+      <c r="I18" s="281"/>
     </row>
     <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="I19" s="292"/>
+      <c r="I19" s="281"/>
     </row>
     <row r="20" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="I20" s="293"/>
+      <c r="I20" s="282"/>
     </row>
     <row r="23" spans="8:9" ht="14" x14ac:dyDescent="0.3">
       <c r="I23" s="50"/>
@@ -5408,7 +5408,7 @@
       <c r="I26" s="50"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5KQVTLCqAIjMId1UjYzXT4327rPlr6+CrgeupOtfD3HacxTzf2lgJCF62UDki/GusKiATNt4Tgfr/mZxZbBzBw==" saltValue="eJMPF5og5ZbkvhwrX0RQOw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="3">
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="H11:H18"/>
@@ -5454,35 +5454,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="258" t="s">
+      <c r="C1" s="256" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="258"/>
+      <c r="D1" s="256"/>
       <c r="E1" s="15"/>
       <c r="S1" s="77"/>
     </row>
     <row r="2" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="298" t="s">
+      <c r="A2" s="287" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="298"/>
-      <c r="C2" s="298"/>
-      <c r="D2" s="298"/>
-      <c r="E2" s="298"/>
-      <c r="F2" s="298"/>
-      <c r="G2" s="298"/>
-      <c r="H2" s="298"/>
-      <c r="I2" s="298"/>
-      <c r="J2" s="298"/>
-      <c r="K2" s="298"/>
-      <c r="L2" s="298"/>
-      <c r="M2" s="298"/>
-      <c r="N2" s="298"/>
-      <c r="O2" s="298"/>
-      <c r="P2" s="298"/>
-      <c r="Q2" s="298"/>
-      <c r="R2" s="298"/>
-      <c r="S2" s="298"/>
+      <c r="B2" s="287"/>
+      <c r="C2" s="287"/>
+      <c r="D2" s="287"/>
+      <c r="E2" s="287"/>
+      <c r="F2" s="287"/>
+      <c r="G2" s="287"/>
+      <c r="H2" s="287"/>
+      <c r="I2" s="287"/>
+      <c r="J2" s="287"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="287"/>
+      <c r="M2" s="287"/>
+      <c r="N2" s="287"/>
+      <c r="O2" s="287"/>
+      <c r="P2" s="287"/>
+      <c r="Q2" s="287"/>
+      <c r="R2" s="287"/>
+      <c r="S2" s="287"/>
     </row>
     <row r="3" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="78"/>
@@ -5591,7 +5591,7 @@
       <c r="B6" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="299" t="str">
+      <c r="C6" s="257" t="str">
         <f>Greitis!C6</f>
         <v>XXXX</v>
       </c>
@@ -5671,7 +5671,7 @@
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="36"/>
       <c r="B7" s="33"/>
-      <c r="C7" s="300"/>
+      <c r="C7" s="258"/>
       <c r="D7" s="17"/>
       <c r="E7" s="18"/>
       <c r="F7" s="181">
@@ -5742,7 +5742,7 @@
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="36"/>
       <c r="B8" s="33"/>
-      <c r="C8" s="300"/>
+      <c r="C8" s="258"/>
       <c r="D8" s="17"/>
       <c r="E8" s="18"/>
       <c r="F8" s="181">
@@ -5813,7 +5813,7 @@
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="36"/>
       <c r="B9" s="33"/>
-      <c r="C9" s="300"/>
+      <c r="C9" s="258"/>
       <c r="D9" s="82"/>
       <c r="E9" s="82"/>
       <c r="F9" s="181">
@@ -5887,7 +5887,7 @@
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="82"/>
       <c r="B10" s="82"/>
-      <c r="C10" s="300"/>
+      <c r="C10" s="258"/>
       <c r="D10" s="82"/>
       <c r="E10" s="82"/>
       <c r="F10" s="181">
@@ -5937,13 +5937,13 @@
       </c>
       <c r="R10" s="82"/>
       <c r="S10" s="82"/>
-      <c r="T10" s="295" t="s">
+      <c r="T10" s="284" t="s">
         <v>30</v>
       </c>
-      <c r="U10" s="295" t="s">
+      <c r="U10" s="284" t="s">
         <v>31</v>
       </c>
-      <c r="V10" s="294" t="s">
+      <c r="V10" s="283" t="s">
         <v>35</v>
       </c>
       <c r="X10" s="232">
@@ -5958,7 +5958,7 @@
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="82"/>
       <c r="B11" s="82"/>
-      <c r="C11" s="300"/>
+      <c r="C11" s="258"/>
       <c r="D11" s="82"/>
       <c r="E11" s="82"/>
       <c r="F11" s="181">
@@ -6008,9 +6008,9 @@
       </c>
       <c r="R11" s="82"/>
       <c r="S11" s="82"/>
-      <c r="T11" s="296"/>
-      <c r="U11" s="296"/>
-      <c r="V11" s="294"/>
+      <c r="T11" s="285"/>
+      <c r="U11" s="285"/>
+      <c r="V11" s="283"/>
       <c r="X11" s="232">
         <f>Greitis!E11</f>
         <v>0.14000000000000001</v>
@@ -6023,7 +6023,7 @@
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="82"/>
       <c r="B12" s="82"/>
-      <c r="C12" s="300"/>
+      <c r="C12" s="258"/>
       <c r="D12" s="82"/>
       <c r="E12" s="82"/>
       <c r="F12" s="181">
@@ -6073,9 +6073,9 @@
       </c>
       <c r="R12" s="82"/>
       <c r="S12" s="82"/>
-      <c r="T12" s="297"/>
-      <c r="U12" s="297"/>
-      <c r="V12" s="294"/>
+      <c r="T12" s="286"/>
+      <c r="U12" s="286"/>
+      <c r="V12" s="283"/>
       <c r="X12" s="232">
         <f>Greitis!E12</f>
         <v>0.14000000000000001</v>
@@ -6088,7 +6088,7 @@
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="82"/>
       <c r="B13" s="82"/>
-      <c r="C13" s="300"/>
+      <c r="C13" s="258"/>
       <c r="D13" s="82"/>
       <c r="E13" s="82"/>
       <c r="F13" s="181">
@@ -6150,7 +6150,7 @@
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="82"/>
       <c r="B14" s="82"/>
-      <c r="C14" s="300"/>
+      <c r="C14" s="258"/>
       <c r="D14" s="82"/>
       <c r="E14" s="82"/>
       <c r="F14" s="181">
@@ -6212,7 +6212,7 @@
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="82"/>
       <c r="B15" s="82"/>
-      <c r="C15" s="300"/>
+      <c r="C15" s="258"/>
       <c r="D15" s="82"/>
       <c r="E15" s="82"/>
       <c r="F15" s="181">
@@ -6274,7 +6274,7 @@
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="82"/>
       <c r="B16" s="82"/>
-      <c r="C16" s="300"/>
+      <c r="C16" s="258"/>
       <c r="D16" s="82"/>
       <c r="E16" s="82"/>
       <c r="F16" s="181">
@@ -6336,7 +6336,7 @@
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="82"/>
       <c r="B17" s="82"/>
-      <c r="C17" s="300"/>
+      <c r="C17" s="258"/>
       <c r="D17" s="82"/>
       <c r="E17" s="82"/>
       <c r="F17" s="181">
@@ -6398,7 +6398,7 @@
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="82"/>
       <c r="B18" s="82"/>
-      <c r="C18" s="300"/>
+      <c r="C18" s="258"/>
       <c r="D18" s="82"/>
       <c r="E18" s="82"/>
       <c r="F18" s="181">
@@ -6460,7 +6460,7 @@
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="82"/>
       <c r="B19" s="82"/>
-      <c r="C19" s="300"/>
+      <c r="C19" s="258"/>
       <c r="D19" s="82"/>
       <c r="E19" s="82"/>
       <c r="F19" s="181">
@@ -6522,7 +6522,7 @@
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="82"/>
       <c r="B20" s="82"/>
-      <c r="C20" s="300"/>
+      <c r="C20" s="258"/>
       <c r="D20" s="82"/>
       <c r="E20" s="82"/>
       <c r="F20" s="181">
@@ -6584,7 +6584,7 @@
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="82"/>
       <c r="B21" s="82"/>
-      <c r="C21" s="300"/>
+      <c r="C21" s="258"/>
       <c r="D21" s="82"/>
       <c r="E21" s="82"/>
       <c r="F21" s="181">
@@ -6646,7 +6646,7 @@
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="83"/>
       <c r="B22" s="83"/>
-      <c r="C22" s="301"/>
+      <c r="C22" s="259"/>
       <c r="D22" s="83"/>
       <c r="E22" s="83"/>
       <c r="F22" s="181">
@@ -6792,26 +6792,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="258" t="s">
+      <c r="C1" s="256" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="258"/>
+      <c r="D1" s="256"/>
       <c r="Q1" s="16"/>
     </row>
     <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="255" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="259"/>
-      <c r="H2" s="259"/>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
-      <c r="M2" s="259"/>
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="255"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="255"/>
+      <c r="M2" s="255"/>
       <c r="Q2" s="16"/>
     </row>
     <row r="3" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -6873,7 +6873,7 @@
         <f>Paėmimas!B6</f>
         <v>XX</v>
       </c>
-      <c r="C6" s="299" t="str">
+      <c r="C6" s="257" t="str">
         <f>Paėmimas!C6</f>
         <v>XXXX</v>
       </c>
@@ -6925,7 +6925,7 @@
     <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="52"/>
       <c r="B7" s="21"/>
-      <c r="C7" s="300"/>
+      <c r="C7" s="258"/>
       <c r="D7" s="187">
         <f>Paėmimas!L7</f>
         <v>0.03</v>
@@ -6962,7 +6962,7 @@
     <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="52"/>
       <c r="B8" s="21"/>
-      <c r="C8" s="300"/>
+      <c r="C8" s="258"/>
       <c r="D8" s="187">
         <f>Paėmimas!L8</f>
         <v>0.03</v>
@@ -6999,7 +6999,7 @@
     <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52"/>
       <c r="B9" s="21"/>
-      <c r="C9" s="300"/>
+      <c r="C9" s="258"/>
       <c r="D9" s="187">
         <f>Paėmimas!L9</f>
         <v>0.03</v>
@@ -7036,7 +7036,7 @@
     <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="52"/>
       <c r="B10" s="21"/>
-      <c r="C10" s="300"/>
+      <c r="C10" s="258"/>
       <c r="D10" s="187">
         <f>Paėmimas!L10</f>
         <v>0.03</v>
@@ -7073,7 +7073,7 @@
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="52"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="300"/>
+      <c r="C11" s="258"/>
       <c r="D11" s="187">
         <f>Paėmimas!L11</f>
         <v>0.03</v>
@@ -7110,7 +7110,7 @@
     <row r="12" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="52"/>
       <c r="B12" s="21"/>
-      <c r="C12" s="300"/>
+      <c r="C12" s="258"/>
       <c r="D12" s="187">
         <f>Paėmimas!L12</f>
         <v>0.03</v>
@@ -7147,7 +7147,7 @@
     <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="52"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="300"/>
+      <c r="C13" s="258"/>
       <c r="D13" s="187">
         <f>Paėmimas!L13</f>
         <v>0.03</v>
@@ -7184,7 +7184,7 @@
     <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="52"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="300"/>
+      <c r="C14" s="258"/>
       <c r="D14" s="187">
         <f>Paėmimas!L14</f>
         <v>0.03</v>
@@ -7221,7 +7221,7 @@
     <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="52"/>
       <c r="B15" s="21"/>
-      <c r="C15" s="300"/>
+      <c r="C15" s="258"/>
       <c r="D15" s="187">
         <f>Paėmimas!L15</f>
         <v>0.03</v>
@@ -7258,7 +7258,7 @@
     <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="52"/>
       <c r="B16" s="21"/>
-      <c r="C16" s="300"/>
+      <c r="C16" s="258"/>
       <c r="D16" s="187">
         <f>Paėmimas!L16</f>
         <v>0.03</v>
@@ -7295,7 +7295,7 @@
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="52"/>
       <c r="B17" s="21"/>
-      <c r="C17" s="300"/>
+      <c r="C17" s="258"/>
       <c r="D17" s="187">
         <f>Paėmimas!L17</f>
         <v>0.03</v>
@@ -7332,7 +7332,7 @@
     <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52"/>
       <c r="B18" s="21"/>
-      <c r="C18" s="300"/>
+      <c r="C18" s="258"/>
       <c r="D18" s="187">
         <f>Paėmimas!L18</f>
         <v>0.03</v>
@@ -7369,7 +7369,7 @@
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="52"/>
       <c r="B19" s="21"/>
-      <c r="C19" s="300"/>
+      <c r="C19" s="258"/>
       <c r="D19" s="187">
         <f>Paėmimas!L19</f>
         <v>0.03</v>
@@ -7406,7 +7406,7 @@
     <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="52"/>
       <c r="B20" s="21"/>
-      <c r="C20" s="300"/>
+      <c r="C20" s="258"/>
       <c r="D20" s="187">
         <f>Paėmimas!L20</f>
         <v>0.03</v>
@@ -7443,7 +7443,7 @@
     <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="52"/>
       <c r="B21" s="21"/>
-      <c r="C21" s="300"/>
+      <c r="C21" s="258"/>
       <c r="D21" s="187">
         <f>Paėmimas!L21</f>
         <v>0.03</v>
@@ -7480,7 +7480,7 @@
     <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="54"/>
       <c r="B22" s="55"/>
-      <c r="C22" s="301"/>
+      <c r="C22" s="259"/>
       <c r="D22" s="187">
         <f>Paėmimas!L22</f>
         <v>0.03</v>
@@ -7566,7 +7566,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="znlurWO2/S7L6Ofr3tZ1B+ubPlnpmXBSnLoh/qKsxBwsnOw0l47v6wJjGD6UwhXH3XbdaiwHSkWP8TS3xUPzJw==" saltValue="PNKv5R93QiSytHI4peHN6Q==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="3">
     <mergeCell ref="C2:M2"/>
     <mergeCell ref="C1:D1"/>
@@ -7611,29 +7611,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="258" t="s">
+      <c r="C1" s="256" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="258"/>
+      <c r="D1" s="256"/>
       <c r="R1" s="16"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="259" t="s">
+      <c r="A2" s="255" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="259"/>
-      <c r="C2" s="259"/>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="259"/>
-      <c r="H2" s="259"/>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
-      <c r="M2" s="259"/>
-      <c r="N2" s="259"/>
+      <c r="B2" s="255"/>
+      <c r="C2" s="255"/>
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="255"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="255"/>
+      <c r="M2" s="255"/>
+      <c r="N2" s="255"/>
       <c r="O2" s="78"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -7704,7 +7704,7 @@
         <f>Svėrimas!A6</f>
         <v>XX</v>
       </c>
-      <c r="C6" s="302" t="str">
+      <c r="C6" s="288" t="str">
         <f>Paėmimas!C6</f>
         <v>XXXX</v>
       </c>
@@ -7763,7 +7763,7 @@
     <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="190"/>
       <c r="B7" s="191"/>
-      <c r="C7" s="302"/>
+      <c r="C7" s="288"/>
       <c r="D7" s="194"/>
       <c r="E7" s="195"/>
       <c r="F7" s="196"/>
@@ -7781,7 +7781,7 @@
     <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="192"/>
       <c r="B8" s="193"/>
-      <c r="C8" s="303"/>
+      <c r="C8" s="289"/>
       <c r="D8" s="194"/>
       <c r="E8" s="195"/>
       <c r="F8" s="196"/>
@@ -7837,77 +7837,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="258" t="s">
+      <c r="C1" s="256" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="258"/>
-      <c r="E1" s="258"/>
-      <c r="F1" s="258"/>
+      <c r="D1" s="256"/>
+      <c r="E1" s="256"/>
+      <c r="F1" s="256"/>
     </row>
     <row r="2" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="259" t="s">
+      <c r="A2" s="255" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="259"/>
-      <c r="C2" s="259"/>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="259"/>
-      <c r="H2" s="259"/>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
-      <c r="M2" s="259"/>
-      <c r="N2" s="259"/>
-      <c r="O2" s="259"/>
+      <c r="B2" s="255"/>
+      <c r="C2" s="255"/>
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="255"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="255"/>
+      <c r="M2" s="255"/>
+      <c r="N2" s="255"/>
+      <c r="O2" s="255"/>
       <c r="V2" s="16"/>
     </row>
     <row r="4" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="261" t="s">
+      <c r="A4" s="294" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="294" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="269" t="s">
+      <c r="C4" s="302" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="269" t="s">
+      <c r="D4" s="302" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="269" t="s">
+      <c r="E4" s="302" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="269" t="s">
+      <c r="F4" s="302"/>
+      <c r="G4" s="302"/>
+      <c r="H4" s="302" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="265" t="s">
+      <c r="I4" s="298" t="s">
         <v>81</v>
       </c>
-      <c r="J4" s="260" t="s">
+      <c r="J4" s="293" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
-      <c r="M4" s="267" t="s">
+      <c r="K4" s="293"/>
+      <c r="L4" s="293"/>
+      <c r="M4" s="300" t="s">
         <v>83</v>
       </c>
-      <c r="N4" s="260" t="s">
+      <c r="N4" s="293" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="263" t="s">
+      <c r="O4" s="296" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="262"/>
-      <c r="B5" s="262"/>
-      <c r="C5" s="270"/>
-      <c r="D5" s="269"/>
+      <c r="A5" s="295"/>
+      <c r="B5" s="295"/>
+      <c r="C5" s="303"/>
+      <c r="D5" s="302"/>
       <c r="E5" s="110">
         <v>1</v>
       </c>
@@ -7917,8 +7917,8 @@
       <c r="G5" s="110">
         <v>3</v>
       </c>
-      <c r="H5" s="269"/>
-      <c r="I5" s="266"/>
+      <c r="H5" s="302"/>
+      <c r="I5" s="299"/>
       <c r="J5" s="12">
         <v>1</v>
       </c>
@@ -7928,16 +7928,16 @@
       <c r="L5" s="12">
         <v>3</v>
       </c>
-      <c r="M5" s="268"/>
-      <c r="N5" s="260"/>
-      <c r="O5" s="264"/>
+      <c r="M5" s="301"/>
+      <c r="N5" s="293"/>
+      <c r="O5" s="297"/>
     </row>
     <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="212" t="str">
         <f>Paėmimas!B6</f>
         <v>XX</v>
       </c>
-      <c r="B6" s="255" t="str">
+      <c r="B6" s="290" t="str">
         <f>Paėmimas!C6</f>
         <v>XXXX</v>
       </c>
@@ -7987,7 +7987,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="213"/>
-      <c r="B7" s="256"/>
+      <c r="B7" s="291"/>
       <c r="C7" s="31"/>
       <c r="D7" s="28"/>
       <c r="E7" s="172"/>
@@ -8007,7 +8007,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="93"/>
-      <c r="B8" s="256"/>
+      <c r="B8" s="291"/>
       <c r="C8" s="31"/>
       <c r="D8" s="28"/>
       <c r="E8" s="172"/>
@@ -8027,7 +8027,7 @@
     </row>
     <row r="9" spans="1:22" ht="17" x14ac:dyDescent="0.45">
       <c r="A9" s="93"/>
-      <c r="B9" s="256"/>
+      <c r="B9" s="291"/>
       <c r="C9" s="31">
         <v>2</v>
       </c>
@@ -8064,7 +8064,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="93"/>
-      <c r="B10" s="256"/>
+      <c r="B10" s="291"/>
       <c r="C10" s="31"/>
       <c r="D10" s="88"/>
       <c r="E10" s="172"/>
@@ -8081,7 +8081,7 @@
     </row>
     <row r="11" spans="1:22" ht="17" x14ac:dyDescent="0.45">
       <c r="A11" s="93"/>
-      <c r="B11" s="256"/>
+      <c r="B11" s="291"/>
       <c r="C11" s="31">
         <v>41</v>
       </c>
@@ -8117,7 +8117,7 @@
     </row>
     <row r="12" spans="1:22" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="93"/>
-      <c r="B12" s="256"/>
+      <c r="B12" s="291"/>
       <c r="C12" s="106" t="s">
         <v>40</v>
       </c>
@@ -8153,7 +8153,7 @@
     </row>
     <row r="13" spans="1:22" ht="17" x14ac:dyDescent="0.45">
       <c r="A13" s="93"/>
-      <c r="B13" s="256"/>
+      <c r="B13" s="291"/>
       <c r="C13" s="107" t="s">
         <v>41</v>
       </c>
@@ -8189,7 +8189,7 @@
     </row>
     <row r="14" spans="1:22" ht="17" x14ac:dyDescent="0.45">
       <c r="A14" s="93"/>
-      <c r="B14" s="256"/>
+      <c r="B14" s="291"/>
       <c r="C14" s="107" t="s">
         <v>42</v>
       </c>
@@ -8225,7 +8225,7 @@
     </row>
     <row r="15" spans="1:22" ht="17" x14ac:dyDescent="0.45">
       <c r="A15" s="93"/>
-      <c r="B15" s="256"/>
+      <c r="B15" s="291"/>
       <c r="C15" s="108" t="s">
         <v>43</v>
       </c>
@@ -8261,7 +8261,7 @@
     </row>
     <row r="16" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="94"/>
-      <c r="B16" s="257"/>
+      <c r="B16" s="292"/>
       <c r="C16" s="31"/>
       <c r="D16" s="90"/>
       <c r="E16" s="19"/>
@@ -8378,6 +8378,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
     <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
@@ -8632,7 +8641,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
@@ -8643,16 +8652,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605DD0A7-BC00-4D8E-8AD3-26E2A9FDEA54}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9703A619-DCB0-4BDF-96BA-CEA752E58475}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8671,7 +8679,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709F4DDD-DF1A-450D-8BF1-976CA47CFD58}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -8680,12 +8688,4 @@
     <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605DD0A7-BC00-4D8E-8AD3-26E2A9FDEA54}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/PVZ2.xlsx
+++ b/PVZ2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="147" documentId="8_{8FD3B17B-922A-42A3-879B-A575A223ADA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D4044E6-60E2-4BF7-BDD4-4F820AD5D73A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="821" firstSheet="1" activeTab="2" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="821" firstSheet="1" activeTab="1" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Compatibility Report" sheetId="4" state="hidden" r:id="rId1"/>
@@ -2658,14 +2658,122 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="29" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2675,115 +2783,7 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="29" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3283,31 +3283,31 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="D3" s="262" t="s">
+      <c r="D3" s="264" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="262"/>
-      <c r="F3" s="262"/>
-      <c r="G3" s="262"/>
-      <c r="H3" s="262"/>
-      <c r="I3" s="262"/>
-      <c r="J3" s="262"/>
-      <c r="K3" s="262"/>
-      <c r="L3" s="262"/>
-      <c r="M3" s="262"/>
-      <c r="N3" s="262"/>
-      <c r="O3" s="262"/>
-      <c r="P3" s="262"/>
-      <c r="Q3" s="262"/>
-      <c r="R3" s="262"/>
-      <c r="S3" s="262"/>
-      <c r="T3" s="262"/>
-      <c r="U3" s="262"/>
-      <c r="V3" s="262"/>
-      <c r="W3" s="262"/>
-      <c r="X3" s="262"/>
-      <c r="Y3" s="262"/>
-      <c r="Z3" s="262"/>
+      <c r="E3" s="264"/>
+      <c r="F3" s="264"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="264"/>
+      <c r="I3" s="264"/>
+      <c r="J3" s="264"/>
+      <c r="K3" s="264"/>
+      <c r="L3" s="264"/>
+      <c r="M3" s="264"/>
+      <c r="N3" s="264"/>
+      <c r="O3" s="264"/>
+      <c r="P3" s="264"/>
+      <c r="Q3" s="264"/>
+      <c r="R3" s="264"/>
+      <c r="S3" s="264"/>
+      <c r="T3" s="264"/>
+      <c r="U3" s="264"/>
+      <c r="V3" s="264"/>
+      <c r="W3" s="264"/>
+      <c r="X3" s="264"/>
+      <c r="Y3" s="264"/>
+      <c r="Z3" s="264"/>
     </row>
     <row r="5" spans="1:28" s="10" customFormat="1" ht="126" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
@@ -3396,13 +3396,13 @@
       </c>
     </row>
     <row r="6" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="263" t="s">
+      <c r="A6" s="265" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="266" t="s">
+      <c r="B6" s="268" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="267" t="s">
+      <c r="C6" s="269" t="s">
         <v>140</v>
       </c>
       <c r="D6" s="127">
@@ -3488,14 +3488,14 @@
         <f>Aerodinamika!G23</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="AB6" s="260" t="s">
+      <c r="AB6" s="262" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="264"/>
-      <c r="B7" s="264"/>
-      <c r="C7" s="268"/>
+      <c r="A7" s="266"/>
+      <c r="B7" s="266"/>
+      <c r="C7" s="270"/>
       <c r="D7" s="127">
         <v>19</v>
       </c>
@@ -3575,12 +3575,12 @@
         <f>O6*X7</f>
         <v>0.34740732161375365</v>
       </c>
-      <c r="AB7" s="261"/>
+      <c r="AB7" s="263"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="264"/>
-      <c r="B8" s="264"/>
-      <c r="C8" s="268"/>
+      <c r="A8" s="266"/>
+      <c r="B8" s="266"/>
+      <c r="C8" s="270"/>
       <c r="D8" s="254">
         <v>33</v>
       </c>
@@ -3626,9 +3626,9 @@
       <c r="S8" s="126"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="264"/>
-      <c r="B9" s="264"/>
-      <c r="C9" s="268"/>
+      <c r="A9" s="266"/>
+      <c r="B9" s="266"/>
+      <c r="C9" s="270"/>
       <c r="D9" s="127">
         <v>48</v>
       </c>
@@ -3678,9 +3678,9 @@
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="264"/>
-      <c r="B10" s="264"/>
-      <c r="C10" s="268"/>
+      <c r="A10" s="266"/>
+      <c r="B10" s="266"/>
+      <c r="C10" s="270"/>
       <c r="D10" s="127">
         <v>65</v>
       </c>
@@ -3719,9 +3719,9 @@
       <c r="N10" s="179"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="264"/>
-      <c r="B11" s="264"/>
-      <c r="C11" s="268"/>
+      <c r="A11" s="266"/>
+      <c r="B11" s="266"/>
+      <c r="C11" s="270"/>
       <c r="D11" s="127">
         <v>85</v>
       </c>
@@ -3760,9 +3760,9 @@
       <c r="N11" s="179"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="264"/>
-      <c r="B12" s="264"/>
-      <c r="C12" s="268"/>
+      <c r="A12" s="266"/>
+      <c r="B12" s="266"/>
+      <c r="C12" s="270"/>
       <c r="D12" s="127">
         <v>108</v>
       </c>
@@ -3801,9 +3801,9 @@
       <c r="N12" s="179"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="264"/>
-      <c r="B13" s="264"/>
-      <c r="C13" s="268"/>
+      <c r="A13" s="266"/>
+      <c r="B13" s="266"/>
+      <c r="C13" s="270"/>
       <c r="D13" s="127">
         <v>140</v>
       </c>
@@ -3843,9 +3843,9 @@
       <c r="O13" s="124"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="264"/>
-      <c r="B14" s="264"/>
-      <c r="C14" s="268"/>
+      <c r="A14" s="266"/>
+      <c r="B14" s="266"/>
+      <c r="C14" s="270"/>
       <c r="D14" s="127">
         <v>200</v>
       </c>
@@ -3888,9 +3888,9 @@
       <c r="U14" s="37"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="264"/>
-      <c r="B15" s="264"/>
-      <c r="C15" s="268"/>
+      <c r="A15" s="266"/>
+      <c r="B15" s="266"/>
+      <c r="C15" s="270"/>
       <c r="D15" s="127">
         <v>260</v>
       </c>
@@ -3933,9 +3933,9 @@
       <c r="U15" s="37"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="264"/>
-      <c r="B16" s="264"/>
-      <c r="C16" s="268"/>
+      <c r="A16" s="266"/>
+      <c r="B16" s="266"/>
+      <c r="C16" s="270"/>
       <c r="D16" s="127">
         <v>292</v>
       </c>
@@ -3978,9 +3978,9 @@
       <c r="U16" s="37"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="264"/>
-      <c r="B17" s="264"/>
-      <c r="C17" s="268"/>
+      <c r="A17" s="266"/>
+      <c r="B17" s="266"/>
+      <c r="C17" s="270"/>
       <c r="D17" s="127">
         <v>315</v>
       </c>
@@ -4023,9 +4023,9 @@
       <c r="U17" s="37"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="264"/>
-      <c r="B18" s="264"/>
-      <c r="C18" s="268"/>
+      <c r="A18" s="266"/>
+      <c r="B18" s="266"/>
+      <c r="C18" s="270"/>
       <c r="D18" s="127">
         <v>335</v>
       </c>
@@ -4068,9 +4068,9 @@
       <c r="U18" s="37"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="264"/>
-      <c r="B19" s="264"/>
-      <c r="C19" s="268"/>
+      <c r="A19" s="266"/>
+      <c r="B19" s="266"/>
+      <c r="C19" s="270"/>
       <c r="D19" s="127">
         <v>352</v>
       </c>
@@ -4113,9 +4113,9 @@
       <c r="U19" s="37"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="264"/>
-      <c r="B20" s="264"/>
-      <c r="C20" s="268"/>
+      <c r="A20" s="266"/>
+      <c r="B20" s="266"/>
+      <c r="C20" s="270"/>
       <c r="D20" s="127">
         <v>367</v>
       </c>
@@ -4158,9 +4158,9 @@
       <c r="U20" s="37"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="264"/>
-      <c r="B21" s="264"/>
-      <c r="C21" s="268"/>
+      <c r="A21" s="266"/>
+      <c r="B21" s="266"/>
+      <c r="C21" s="270"/>
       <c r="D21" s="127">
         <v>381</v>
       </c>
@@ -4203,9 +4203,9 @@
       <c r="U21" s="37"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="265"/>
-      <c r="B22" s="265"/>
-      <c r="C22" s="269"/>
+      <c r="A22" s="267"/>
+      <c r="B22" s="267"/>
+      <c r="C22" s="271"/>
       <c r="D22" s="127">
         <v>394</v>
       </c>
@@ -4309,11 +4309,11 @@
         <v>0</v>
       </c>
       <c r="N24" s="69"/>
-      <c r="O24" s="270" t="s">
+      <c r="O24" s="272" t="s">
         <v>127</v>
       </c>
-      <c r="P24" s="271"/>
-      <c r="Q24" s="271"/>
+      <c r="P24" s="273"/>
+      <c r="Q24" s="273"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="157"/>
@@ -4348,30 +4348,30 @@
       <c r="A28" s="157"/>
       <c r="B28" s="157"/>
       <c r="C28" s="157"/>
-      <c r="D28" s="272" t="s">
+      <c r="D28" s="274" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="262"/>
-      <c r="F28" s="262"/>
-      <c r="G28" s="262"/>
-      <c r="H28" s="262"/>
-      <c r="I28" s="262"/>
-      <c r="J28" s="262"/>
-      <c r="K28" s="262"/>
-      <c r="L28" s="262"/>
-      <c r="M28" s="262"/>
-      <c r="N28" s="262"/>
-      <c r="O28" s="262"/>
-      <c r="P28" s="262"/>
-      <c r="Q28" s="262"/>
-      <c r="R28" s="262"/>
-      <c r="S28" s="262"/>
-      <c r="T28" s="262"/>
-      <c r="U28" s="262"/>
-      <c r="V28" s="262"/>
-      <c r="W28" s="262"/>
-      <c r="X28" s="262"/>
-      <c r="Y28" s="262"/>
+      <c r="E28" s="264"/>
+      <c r="F28" s="264"/>
+      <c r="G28" s="264"/>
+      <c r="H28" s="264"/>
+      <c r="I28" s="264"/>
+      <c r="J28" s="264"/>
+      <c r="K28" s="264"/>
+      <c r="L28" s="264"/>
+      <c r="M28" s="264"/>
+      <c r="N28" s="264"/>
+      <c r="O28" s="264"/>
+      <c r="P28" s="264"/>
+      <c r="Q28" s="264"/>
+      <c r="R28" s="264"/>
+      <c r="S28" s="264"/>
+      <c r="T28" s="264"/>
+      <c r="U28" s="264"/>
+      <c r="V28" s="264"/>
+      <c r="W28" s="264"/>
+      <c r="X28" s="264"/>
+      <c r="Y28" s="264"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="157"/>
@@ -4476,9 +4476,9 @@
       </c>
     </row>
     <row r="31" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="273"/>
-      <c r="B31" s="273"/>
-      <c r="C31" s="273"/>
+      <c r="A31" s="275"/>
+      <c r="B31" s="275"/>
+      <c r="C31" s="275"/>
       <c r="D31" s="127">
         <v>6</v>
       </c>
@@ -4556,12 +4556,12 @@
         <f>Aerodinamika!G23</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="AB31" s="260"/>
+      <c r="AB31" s="262"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A32" s="274"/>
-      <c r="B32" s="274"/>
-      <c r="C32" s="274"/>
+      <c r="A32" s="276"/>
+      <c r="B32" s="276"/>
+      <c r="C32" s="276"/>
       <c r="D32" s="127">
         <v>19</v>
       </c>
@@ -4632,12 +4632,12 @@
         <f>O31*X32</f>
         <v>0.34740732161375365</v>
       </c>
-      <c r="AB32" s="261"/>
+      <c r="AB32" s="263"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A33" s="274"/>
-      <c r="B33" s="274"/>
-      <c r="C33" s="274"/>
+      <c r="A33" s="276"/>
+      <c r="B33" s="276"/>
+      <c r="C33" s="276"/>
       <c r="D33" s="254">
         <v>33</v>
       </c>
@@ -4674,9 +4674,9 @@
       <c r="S33" s="126"/>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A34" s="274"/>
-      <c r="B34" s="274"/>
-      <c r="C34" s="274"/>
+      <c r="A34" s="276"/>
+      <c r="B34" s="276"/>
+      <c r="C34" s="276"/>
       <c r="D34" s="127">
         <v>48</v>
       </c>
@@ -4717,9 +4717,9 @@
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A35" s="274"/>
-      <c r="B35" s="274"/>
-      <c r="C35" s="274"/>
+      <c r="A35" s="276"/>
+      <c r="B35" s="276"/>
+      <c r="C35" s="276"/>
       <c r="D35" s="127">
         <v>65</v>
       </c>
@@ -4749,9 +4749,9 @@
       <c r="N35" s="133"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A36" s="274"/>
-      <c r="B36" s="274"/>
-      <c r="C36" s="274"/>
+      <c r="A36" s="276"/>
+      <c r="B36" s="276"/>
+      <c r="C36" s="276"/>
       <c r="D36" s="127">
         <v>85</v>
       </c>
@@ -4781,9 +4781,9 @@
       <c r="N36" s="133"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A37" s="274"/>
-      <c r="B37" s="274"/>
-      <c r="C37" s="274"/>
+      <c r="A37" s="276"/>
+      <c r="B37" s="276"/>
+      <c r="C37" s="276"/>
       <c r="D37" s="127">
         <v>108</v>
       </c>
@@ -4813,9 +4813,9 @@
       <c r="N37" s="133"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A38" s="274"/>
-      <c r="B38" s="274"/>
-      <c r="C38" s="274"/>
+      <c r="A38" s="276"/>
+      <c r="B38" s="276"/>
+      <c r="C38" s="276"/>
       <c r="D38" s="127">
         <v>140</v>
       </c>
@@ -4846,9 +4846,9 @@
       <c r="O38" s="124"/>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A39" s="274"/>
-      <c r="B39" s="274"/>
-      <c r="C39" s="274"/>
+      <c r="A39" s="276"/>
+      <c r="B39" s="276"/>
+      <c r="C39" s="276"/>
       <c r="D39" s="127">
         <v>200</v>
       </c>
@@ -4882,9 +4882,9 @@
       <c r="U39" s="37"/>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A40" s="274"/>
-      <c r="B40" s="274"/>
-      <c r="C40" s="274"/>
+      <c r="A40" s="276"/>
+      <c r="B40" s="276"/>
+      <c r="C40" s="276"/>
       <c r="D40" s="127">
         <v>260</v>
       </c>
@@ -4914,9 +4914,9 @@
       <c r="N40" s="127"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A41" s="274"/>
-      <c r="B41" s="274"/>
-      <c r="C41" s="274"/>
+      <c r="A41" s="276"/>
+      <c r="B41" s="276"/>
+      <c r="C41" s="276"/>
       <c r="D41" s="127">
         <v>292</v>
       </c>
@@ -4946,9 +4946,9 @@
       <c r="N41" s="127"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A42" s="274"/>
-      <c r="B42" s="274"/>
-      <c r="C42" s="274"/>
+      <c r="A42" s="276"/>
+      <c r="B42" s="276"/>
+      <c r="C42" s="276"/>
       <c r="D42" s="127">
         <v>315</v>
       </c>
@@ -4978,9 +4978,9 @@
       <c r="N42" s="127"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A43" s="274"/>
-      <c r="B43" s="274"/>
-      <c r="C43" s="274"/>
+      <c r="A43" s="276"/>
+      <c r="B43" s="276"/>
+      <c r="C43" s="276"/>
       <c r="D43" s="127">
         <v>335</v>
       </c>
@@ -5010,9 +5010,9 @@
       <c r="N43" s="127"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A44" s="274"/>
-      <c r="B44" s="274"/>
-      <c r="C44" s="274"/>
+      <c r="A44" s="276"/>
+      <c r="B44" s="276"/>
+      <c r="C44" s="276"/>
       <c r="D44" s="127">
         <v>352</v>
       </c>
@@ -5042,9 +5042,9 @@
       <c r="N44" s="127"/>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A45" s="274"/>
-      <c r="B45" s="274"/>
-      <c r="C45" s="274"/>
+      <c r="A45" s="276"/>
+      <c r="B45" s="276"/>
+      <c r="C45" s="276"/>
       <c r="D45" s="127">
         <v>367</v>
       </c>
@@ -5074,9 +5074,9 @@
       <c r="N45" s="127"/>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A46" s="274"/>
-      <c r="B46" s="274"/>
-      <c r="C46" s="274"/>
+      <c r="A46" s="276"/>
+      <c r="B46" s="276"/>
+      <c r="C46" s="276"/>
       <c r="D46" s="127">
         <v>381</v>
       </c>
@@ -5106,9 +5106,9 @@
       <c r="N46" s="127"/>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A47" s="275"/>
-      <c r="B47" s="275"/>
-      <c r="C47" s="275"/>
+      <c r="A47" s="277"/>
+      <c r="B47" s="277"/>
+      <c r="C47" s="277"/>
       <c r="D47" s="127">
         <v>394</v>
       </c>
@@ -5196,18 +5196,18 @@
       <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A3" s="276" t="s">
+      <c r="A3" s="255" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="276"/>
-      <c r="C3" s="276"/>
-      <c r="D3" s="276"/>
-      <c r="E3" s="276"/>
-      <c r="F3" s="276"/>
-      <c r="G3" s="276"/>
-      <c r="H3" s="276"/>
-      <c r="I3" s="276"/>
-      <c r="J3" s="276"/>
+      <c r="B3" s="255"/>
+      <c r="C3" s="255"/>
+      <c r="D3" s="255"/>
+      <c r="E3" s="255"/>
+      <c r="F3" s="255"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="255"/>
+      <c r="I3" s="255"/>
+      <c r="J3" s="255"/>
     </row>
     <row r="4" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
@@ -5354,46 +5354,46 @@
       <c r="L10" s="44"/>
     </row>
     <row r="11" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H11" s="277" t="s">
+      <c r="H11" s="256" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="280" t="s">
+      <c r="I11" s="259" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H12" s="278"/>
-      <c r="I12" s="281"/>
+      <c r="H12" s="257"/>
+      <c r="I12" s="260"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H13" s="278"/>
-      <c r="I13" s="281"/>
+      <c r="H13" s="257"/>
+      <c r="I13" s="260"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H14" s="278"/>
-      <c r="I14" s="281"/>
+      <c r="H14" s="257"/>
+      <c r="I14" s="260"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H15" s="278"/>
-      <c r="I15" s="281"/>
+      <c r="H15" s="257"/>
+      <c r="I15" s="260"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H16" s="278"/>
-      <c r="I16" s="281"/>
+      <c r="H16" s="257"/>
+      <c r="I16" s="260"/>
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="278"/>
-      <c r="I17" s="281"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="260"/>
     </row>
     <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="279"/>
-      <c r="I18" s="281"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="260"/>
     </row>
     <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="I19" s="281"/>
+      <c r="I19" s="260"/>
     </row>
     <row r="20" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="I20" s="282"/>
+      <c r="I20" s="261"/>
     </row>
     <row r="23" spans="8:9" ht="14" x14ac:dyDescent="0.3">
       <c r="I23" s="50"/>
@@ -5454,35 +5454,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="256" t="s">
+      <c r="C1" s="282" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="256"/>
+      <c r="D1" s="282"/>
       <c r="E1" s="15"/>
       <c r="S1" s="77"/>
     </row>
     <row r="2" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="287" t="s">
+      <c r="A2" s="283" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="287"/>
-      <c r="C2" s="287"/>
-      <c r="D2" s="287"/>
-      <c r="E2" s="287"/>
-      <c r="F2" s="287"/>
-      <c r="G2" s="287"/>
-      <c r="H2" s="287"/>
-      <c r="I2" s="287"/>
-      <c r="J2" s="287"/>
-      <c r="K2" s="287"/>
-      <c r="L2" s="287"/>
-      <c r="M2" s="287"/>
-      <c r="N2" s="287"/>
-      <c r="O2" s="287"/>
-      <c r="P2" s="287"/>
-      <c r="Q2" s="287"/>
-      <c r="R2" s="287"/>
-      <c r="S2" s="287"/>
+      <c r="B2" s="283"/>
+      <c r="C2" s="283"/>
+      <c r="D2" s="283"/>
+      <c r="E2" s="283"/>
+      <c r="F2" s="283"/>
+      <c r="G2" s="283"/>
+      <c r="H2" s="283"/>
+      <c r="I2" s="283"/>
+      <c r="J2" s="283"/>
+      <c r="K2" s="283"/>
+      <c r="L2" s="283"/>
+      <c r="M2" s="283"/>
+      <c r="N2" s="283"/>
+      <c r="O2" s="283"/>
+      <c r="P2" s="283"/>
+      <c r="Q2" s="283"/>
+      <c r="R2" s="283"/>
+      <c r="S2" s="283"/>
     </row>
     <row r="3" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="78"/>
@@ -5591,7 +5591,7 @@
       <c r="B6" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="257" t="str">
+      <c r="C6" s="284" t="str">
         <f>Greitis!C6</f>
         <v>XXXX</v>
       </c>
@@ -5671,7 +5671,7 @@
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="36"/>
       <c r="B7" s="33"/>
-      <c r="C7" s="258"/>
+      <c r="C7" s="285"/>
       <c r="D7" s="17"/>
       <c r="E7" s="18"/>
       <c r="F7" s="181">
@@ -5742,7 +5742,7 @@
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="36"/>
       <c r="B8" s="33"/>
-      <c r="C8" s="258"/>
+      <c r="C8" s="285"/>
       <c r="D8" s="17"/>
       <c r="E8" s="18"/>
       <c r="F8" s="181">
@@ -5813,7 +5813,7 @@
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="36"/>
       <c r="B9" s="33"/>
-      <c r="C9" s="258"/>
+      <c r="C9" s="285"/>
       <c r="D9" s="82"/>
       <c r="E9" s="82"/>
       <c r="F9" s="181">
@@ -5887,7 +5887,7 @@
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="82"/>
       <c r="B10" s="82"/>
-      <c r="C10" s="258"/>
+      <c r="C10" s="285"/>
       <c r="D10" s="82"/>
       <c r="E10" s="82"/>
       <c r="F10" s="181">
@@ -5937,13 +5937,13 @@
       </c>
       <c r="R10" s="82"/>
       <c r="S10" s="82"/>
-      <c r="T10" s="284" t="s">
+      <c r="T10" s="279" t="s">
         <v>30</v>
       </c>
-      <c r="U10" s="284" t="s">
+      <c r="U10" s="279" t="s">
         <v>31</v>
       </c>
-      <c r="V10" s="283" t="s">
+      <c r="V10" s="278" t="s">
         <v>35</v>
       </c>
       <c r="X10" s="232">
@@ -5958,7 +5958,7 @@
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="82"/>
       <c r="B11" s="82"/>
-      <c r="C11" s="258"/>
+      <c r="C11" s="285"/>
       <c r="D11" s="82"/>
       <c r="E11" s="82"/>
       <c r="F11" s="181">
@@ -6008,9 +6008,9 @@
       </c>
       <c r="R11" s="82"/>
       <c r="S11" s="82"/>
-      <c r="T11" s="285"/>
-      <c r="U11" s="285"/>
-      <c r="V11" s="283"/>
+      <c r="T11" s="280"/>
+      <c r="U11" s="280"/>
+      <c r="V11" s="278"/>
       <c r="X11" s="232">
         <f>Greitis!E11</f>
         <v>0.14000000000000001</v>
@@ -6023,7 +6023,7 @@
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="82"/>
       <c r="B12" s="82"/>
-      <c r="C12" s="258"/>
+      <c r="C12" s="285"/>
       <c r="D12" s="82"/>
       <c r="E12" s="82"/>
       <c r="F12" s="181">
@@ -6073,9 +6073,9 @@
       </c>
       <c r="R12" s="82"/>
       <c r="S12" s="82"/>
-      <c r="T12" s="286"/>
-      <c r="U12" s="286"/>
-      <c r="V12" s="283"/>
+      <c r="T12" s="281"/>
+      <c r="U12" s="281"/>
+      <c r="V12" s="278"/>
       <c r="X12" s="232">
         <f>Greitis!E12</f>
         <v>0.14000000000000001</v>
@@ -6088,7 +6088,7 @@
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="82"/>
       <c r="B13" s="82"/>
-      <c r="C13" s="258"/>
+      <c r="C13" s="285"/>
       <c r="D13" s="82"/>
       <c r="E13" s="82"/>
       <c r="F13" s="181">
@@ -6150,7 +6150,7 @@
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="82"/>
       <c r="B14" s="82"/>
-      <c r="C14" s="258"/>
+      <c r="C14" s="285"/>
       <c r="D14" s="82"/>
       <c r="E14" s="82"/>
       <c r="F14" s="181">
@@ -6212,7 +6212,7 @@
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="82"/>
       <c r="B15" s="82"/>
-      <c r="C15" s="258"/>
+      <c r="C15" s="285"/>
       <c r="D15" s="82"/>
       <c r="E15" s="82"/>
       <c r="F15" s="181">
@@ -6274,7 +6274,7 @@
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="82"/>
       <c r="B16" s="82"/>
-      <c r="C16" s="258"/>
+      <c r="C16" s="285"/>
       <c r="D16" s="82"/>
       <c r="E16" s="82"/>
       <c r="F16" s="181">
@@ -6336,7 +6336,7 @@
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="82"/>
       <c r="B17" s="82"/>
-      <c r="C17" s="258"/>
+      <c r="C17" s="285"/>
       <c r="D17" s="82"/>
       <c r="E17" s="82"/>
       <c r="F17" s="181">
@@ -6398,7 +6398,7 @@
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="82"/>
       <c r="B18" s="82"/>
-      <c r="C18" s="258"/>
+      <c r="C18" s="285"/>
       <c r="D18" s="82"/>
       <c r="E18" s="82"/>
       <c r="F18" s="181">
@@ -6460,7 +6460,7 @@
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="82"/>
       <c r="B19" s="82"/>
-      <c r="C19" s="258"/>
+      <c r="C19" s="285"/>
       <c r="D19" s="82"/>
       <c r="E19" s="82"/>
       <c r="F19" s="181">
@@ -6522,7 +6522,7 @@
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="82"/>
       <c r="B20" s="82"/>
-      <c r="C20" s="258"/>
+      <c r="C20" s="285"/>
       <c r="D20" s="82"/>
       <c r="E20" s="82"/>
       <c r="F20" s="181">
@@ -6584,7 +6584,7 @@
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="82"/>
       <c r="B21" s="82"/>
-      <c r="C21" s="258"/>
+      <c r="C21" s="285"/>
       <c r="D21" s="82"/>
       <c r="E21" s="82"/>
       <c r="F21" s="181">
@@ -6646,7 +6646,7 @@
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="83"/>
       <c r="B22" s="83"/>
-      <c r="C22" s="259"/>
+      <c r="C22" s="286"/>
       <c r="D22" s="83"/>
       <c r="E22" s="83"/>
       <c r="F22" s="181">
@@ -6792,26 +6792,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="256" t="s">
+      <c r="C1" s="282" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="256"/>
+      <c r="D1" s="282"/>
       <c r="Q1" s="16"/>
     </row>
     <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="255" t="s">
+      <c r="C2" s="287" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="255"/>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="255"/>
-      <c r="M2" s="255"/>
+      <c r="D2" s="287"/>
+      <c r="E2" s="287"/>
+      <c r="F2" s="287"/>
+      <c r="G2" s="287"/>
+      <c r="H2" s="287"/>
+      <c r="I2" s="287"/>
+      <c r="J2" s="287"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="287"/>
+      <c r="M2" s="287"/>
       <c r="Q2" s="16"/>
     </row>
     <row r="3" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -6873,7 +6873,7 @@
         <f>Paėmimas!B6</f>
         <v>XX</v>
       </c>
-      <c r="C6" s="257" t="str">
+      <c r="C6" s="284" t="str">
         <f>Paėmimas!C6</f>
         <v>XXXX</v>
       </c>
@@ -6925,7 +6925,7 @@
     <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="52"/>
       <c r="B7" s="21"/>
-      <c r="C7" s="258"/>
+      <c r="C7" s="285"/>
       <c r="D7" s="187">
         <f>Paėmimas!L7</f>
         <v>0.03</v>
@@ -6962,7 +6962,7 @@
     <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="52"/>
       <c r="B8" s="21"/>
-      <c r="C8" s="258"/>
+      <c r="C8" s="285"/>
       <c r="D8" s="187">
         <f>Paėmimas!L8</f>
         <v>0.03</v>
@@ -6999,7 +6999,7 @@
     <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52"/>
       <c r="B9" s="21"/>
-      <c r="C9" s="258"/>
+      <c r="C9" s="285"/>
       <c r="D9" s="187">
         <f>Paėmimas!L9</f>
         <v>0.03</v>
@@ -7036,7 +7036,7 @@
     <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="52"/>
       <c r="B10" s="21"/>
-      <c r="C10" s="258"/>
+      <c r="C10" s="285"/>
       <c r="D10" s="187">
         <f>Paėmimas!L10</f>
         <v>0.03</v>
@@ -7073,7 +7073,7 @@
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="52"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="258"/>
+      <c r="C11" s="285"/>
       <c r="D11" s="187">
         <f>Paėmimas!L11</f>
         <v>0.03</v>
@@ -7110,7 +7110,7 @@
     <row r="12" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="52"/>
       <c r="B12" s="21"/>
-      <c r="C12" s="258"/>
+      <c r="C12" s="285"/>
       <c r="D12" s="187">
         <f>Paėmimas!L12</f>
         <v>0.03</v>
@@ -7147,7 +7147,7 @@
     <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="52"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="258"/>
+      <c r="C13" s="285"/>
       <c r="D13" s="187">
         <f>Paėmimas!L13</f>
         <v>0.03</v>
@@ -7184,7 +7184,7 @@
     <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="52"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="258"/>
+      <c r="C14" s="285"/>
       <c r="D14" s="187">
         <f>Paėmimas!L14</f>
         <v>0.03</v>
@@ -7221,7 +7221,7 @@
     <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="52"/>
       <c r="B15" s="21"/>
-      <c r="C15" s="258"/>
+      <c r="C15" s="285"/>
       <c r="D15" s="187">
         <f>Paėmimas!L15</f>
         <v>0.03</v>
@@ -7258,7 +7258,7 @@
     <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="52"/>
       <c r="B16" s="21"/>
-      <c r="C16" s="258"/>
+      <c r="C16" s="285"/>
       <c r="D16" s="187">
         <f>Paėmimas!L16</f>
         <v>0.03</v>
@@ -7295,7 +7295,7 @@
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="52"/>
       <c r="B17" s="21"/>
-      <c r="C17" s="258"/>
+      <c r="C17" s="285"/>
       <c r="D17" s="187">
         <f>Paėmimas!L17</f>
         <v>0.03</v>
@@ -7332,7 +7332,7 @@
     <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52"/>
       <c r="B18" s="21"/>
-      <c r="C18" s="258"/>
+      <c r="C18" s="285"/>
       <c r="D18" s="187">
         <f>Paėmimas!L18</f>
         <v>0.03</v>
@@ -7369,7 +7369,7 @@
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="52"/>
       <c r="B19" s="21"/>
-      <c r="C19" s="258"/>
+      <c r="C19" s="285"/>
       <c r="D19" s="187">
         <f>Paėmimas!L19</f>
         <v>0.03</v>
@@ -7406,7 +7406,7 @@
     <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="52"/>
       <c r="B20" s="21"/>
-      <c r="C20" s="258"/>
+      <c r="C20" s="285"/>
       <c r="D20" s="187">
         <f>Paėmimas!L20</f>
         <v>0.03</v>
@@ -7443,7 +7443,7 @@
     <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="52"/>
       <c r="B21" s="21"/>
-      <c r="C21" s="258"/>
+      <c r="C21" s="285"/>
       <c r="D21" s="187">
         <f>Paėmimas!L21</f>
         <v>0.03</v>
@@ -7480,7 +7480,7 @@
     <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="54"/>
       <c r="B22" s="55"/>
-      <c r="C22" s="259"/>
+      <c r="C22" s="286"/>
       <c r="D22" s="187">
         <f>Paėmimas!L22</f>
         <v>0.03</v>
@@ -7611,29 +7611,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="256" t="s">
+      <c r="C1" s="282" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="256"/>
+      <c r="D1" s="282"/>
       <c r="R1" s="16"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="255" t="s">
+      <c r="A2" s="287" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="255"/>
-      <c r="C2" s="255"/>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="255"/>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="255"/>
-      <c r="M2" s="255"/>
-      <c r="N2" s="255"/>
+      <c r="B2" s="287"/>
+      <c r="C2" s="287"/>
+      <c r="D2" s="287"/>
+      <c r="E2" s="287"/>
+      <c r="F2" s="287"/>
+      <c r="G2" s="287"/>
+      <c r="H2" s="287"/>
+      <c r="I2" s="287"/>
+      <c r="J2" s="287"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="287"/>
+      <c r="M2" s="287"/>
+      <c r="N2" s="287"/>
       <c r="O2" s="78"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -7837,31 +7837,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="256" t="s">
+      <c r="C1" s="282" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="256"/>
-      <c r="E1" s="256"/>
-      <c r="F1" s="256"/>
+      <c r="D1" s="282"/>
+      <c r="E1" s="282"/>
+      <c r="F1" s="282"/>
     </row>
     <row r="2" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="255" t="s">
+      <c r="A2" s="287" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="255"/>
-      <c r="C2" s="255"/>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="255"/>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="255"/>
-      <c r="M2" s="255"/>
-      <c r="N2" s="255"/>
-      <c r="O2" s="255"/>
+      <c r="B2" s="287"/>
+      <c r="C2" s="287"/>
+      <c r="D2" s="287"/>
+      <c r="E2" s="287"/>
+      <c r="F2" s="287"/>
+      <c r="G2" s="287"/>
+      <c r="H2" s="287"/>
+      <c r="I2" s="287"/>
+      <c r="J2" s="287"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="287"/>
+      <c r="M2" s="287"/>
+      <c r="N2" s="287"/>
+      <c r="O2" s="287"/>
       <c r="V2" s="16"/>
     </row>
     <row r="4" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -8378,12 +8378,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8642,20 +8644,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605DD0A7-BC00-4D8E-8AD3-26E2A9FDEA54}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709F4DDD-DF1A-450D-8BF1-976CA47CFD58}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8680,12 +8683,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709F4DDD-DF1A-450D-8BF1-976CA47CFD58}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605DD0A7-BC00-4D8E-8AD3-26E2A9FDEA54}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
-    <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>